--- a/sales_order_forms/021_marker_order_and_layout_approval_form--sales_order_forms.xlsx
+++ b/sales_order_forms/021_marker_order_and_layout_approval_form--sales_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'landscape'}</t>
+          <t>landscape</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Landscape'}</t>
+          <t>Landscape</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'portrait'}</t>
+          <t>portrait</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Portrait'}</t>
+          <t>Portrait</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'square'}</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Square'}</t>
+          <t>Square</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
